--- a/ADJY_Proje_Faz_Raporu.xlsx
+++ b/ADJY_Proje_Faz_Raporu.xlsx
@@ -612,7 +612,7 @@
         <v>Performans, SEO &amp; Production</v>
       </c>
       <c r="C11" t="str">
-        <v>📋 Planlandı</v>
+        <v>Tamamlandı</v>
       </c>
       <c r="D11" t="str">
         <v>0%</v>
